--- a/Tabellen/Anatomie 1-Muskeln Detail-Oberschenkel-Adduktoren.xlsx
+++ b/Tabellen/Anatomie 1-Muskeln Detail-Oberschenkel-Adduktoren.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Linea aspera Labium mediale</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;70°: Adduktion; &lt;70°: Flexion; &gt;80° Extension; Stabil Frontalebene; Stabil Sagittalebene  </t>
+    <t xml:space="preserve">&lt;70°: Adduktion; &lt;70°: Flexion; &gt;80°: Extension; Stabil Frontalebene; Stabil Sagittalebene  </t>
   </si>
   <si>
     <t xml:space="preserve">M. adductor brevis</t>
@@ -110,7 +110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,12 +140,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -189,7 +183,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -207,10 +201,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -435,7 +425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -452,7 +442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -493,7 +483,7 @@
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -503,11 +493,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="46.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">

--- a/Tabellen/Anatomie 1-Muskeln Detail-Oberschenkel-Adduktoren.xlsx
+++ b/Tabellen/Anatomie 1-Muskeln Detail-Oberschenkel-Adduktoren.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t xml:space="preserve">Außenseite Membrana obturatoria und Knochen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fossa trochanterica Femur</t>
   </si>
   <si>
     <t xml:space="preserve">Adduktion; Außenrotation;  Stabil Sagittalebene</t>
@@ -433,98 +436,98 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
